--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1A6619C-4732-4288-B320-CC5A862798C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9532F06-5D9F-4C89-88D5-AA8CA79C10FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,6 +199,30 @@
   </si>
   <si>
     <t>average day</t>
+  </si>
+  <si>
+    <t>Poonam</t>
+  </si>
+  <si>
+    <t>msc(It)</t>
+  </si>
+  <si>
+    <t>august</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>happy day</t>
   </si>
 </sst>
 </file>
@@ -885,26 +909,34 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>54</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12603282</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1016,48 +1048,95 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7" s="14">
+        <v>300</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14">
+        <v>30</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J7" s="15">
+        <v>40</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>15</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14">
+        <v>120</v>
+      </c>
+      <c r="G8" s="14">
+        <v>3</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>765</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>675</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9532F06-5D9F-4C89-88D5-AA8CA79C10FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1689C01C-7E5C-4F15-9F3C-88281A6952BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1139,26 +1139,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>15</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>40</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>655</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>785</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1689C01C-7E5C-4F15-9F3C-88281A6952BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC3B48E-2083-4FAC-A218-06049590A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1185,26 +1185,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC3B48E-2083-4FAC-A218-06049590A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8EFAB6-1D3F-4C2C-8463-A18004FD2652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>happy day</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -1231,26 +1234,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>35</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>505</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8EFAB6-1D3F-4C2C-8463-A18004FD2652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E24C73F-727F-4E77-872B-35A011CADEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1280,26 +1280,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>40</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>20</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E24C73F-727F-4E77-872B-35A011CADEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C890EF-EE32-4F81-90BD-51EDFE50B74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1326,26 +1329,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>15</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>555</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>885</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12603282(1).xlsx
+++ b/12603282(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C890EF-EE32-4F81-90BD-51EDFE50B74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83620AA4-AA0C-4E2D-B2E4-E52351F27643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1375,26 +1375,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>15</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>30</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>675</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>765</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
